--- a/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
+++ b/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Round 6 · Yogurt pilot - Round 6 to score · Printed 2026-10-04</t>
+          <t>Round 6 · Yogurt pilot - Round 6 to score</t>
         </is>
       </c>
     </row>

--- a/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
+++ b/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Round overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Preparation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="_FoodOptimizer" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet name="Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_FoodOptimizer" sheetId="3" state="veryHidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,7 +543,7 @@
     <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Use the sheet tabs: Round overview → Preparation → Results. Tabs are at the bottom in Excel and at the top in Numbers. Review the plan, prepare each formulation separately, then enter measurements on Results and upload this file in the app.</t>
+          <t>Use the sheet tabs: Round overview → Results. Tabs are at the bottom in Excel and at the top in Numbers. Review the plan, prepare each formulation separately, then enter measurements on Results and upload this file in the app.</t>
         </is>
       </c>
     </row>
@@ -888,11 +887,6 @@
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
@@ -913,8 +907,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A25" location="'Round overview'!A1"/>
-    <hyperlink ref="B25" location="'Preparation'!A1"/>
-    <hyperlink ref="C25" location="'Results'!A1"/>
+    <hyperlink ref="B25" location="'Results'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -922,80 +915,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Preparation — Pre-mixes for this round</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="65" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Use the sheet tabs: Round overview → Preparation → Results. Tabs are at the bottom in Excel and at the top in Numbers. Prepare pre-mixes with fixed ingredient percentages here. For blends where ingredient amounts vary separately, follow the individual amounts on Round overview.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>No pre-mixes are required. Follow the method on Round overview.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Round overview</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>If a link does not open, select the sheet tab with the same name.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A7" location="'Round overview'!A1"/>
-    <hyperlink ref="B7" location="'Preparation'!A1"/>
-    <hyperlink ref="C7" location="'Results'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1023,7 +942,7 @@
     <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Use the sheet tabs: Round overview → Preparation → Results. Tabs are at the bottom in Excel and at the top in Numbers. Each formulation has its own column. Blank means not recorded yet. Enter results, then upload this workbook, check the import and save in the app.</t>
+          <t>Use the sheet tabs: Round overview → Results. Tabs are at the bottom in Excel and at the top in Numbers. Each formulation has its own column. Blank means not recorded yet. Enter results, then upload this workbook, check the import and save in the app.</t>
         </is>
       </c>
     </row>
@@ -1204,6 +1123,8 @@
       <c r="D15" s="15" t="n"/>
       <c r="F15" s="15" t="n"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
@@ -1211,11 +1132,6 @@
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
@@ -1236,15 +1152,14 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A18" location="'Round overview'!A1"/>
-    <hyperlink ref="B18" location="'Preparation'!A1"/>
-    <hyperlink ref="D18" location="'Results'!A1"/>
+    <hyperlink ref="B18" location="'Results'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
+++ b/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tangy (/15) · Target 5</t>
+          <t>Tanginess (/15) · Target 5</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
@@ -1041,7 +1041,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Thickness uniformity (/15) · Target 13</t>
+          <t>Uniformity (/15) · Target 13</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">

--- a/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
+++ b/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Pilot batch 6.1 · EGBO</t>
+          <t>Engine's pick 6.1</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Pilot batch 6.2 · EGBO</t>
+          <t>Engine's pick 6.2</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>Pilot batch 6.3 · EGBO</t>
+          <t>Engine's pick 6.3</t>
         </is>
       </c>
     </row>

--- a/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
+++ b/data/samples/yogurt_pilot/Round 6 results (pilot).xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Total for this round (g)</t>
+          <t>Total for this Round (g)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Across every formulation; a calculated row's total is what the round comes to, not one weighing.</t>
+          <t>Across every formulation; a calculated row's total is what the Round comes to, not one weighing.</t>
         </is>
       </c>
     </row>
